--- a/ValueSet-mii-vs-icu-code-oservation-pupillenform-loinc.xlsx
+++ b/ValueSet-mii-vs-icu-code-oservation-pupillenform-loinc.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T06:46:19+00:00</t>
+    <t>2026-09-15T22:20:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-icu-code-oservation-pupillenform-loinc.xlsx
+++ b/ValueSet-mii-vs-icu-code-oservation-pupillenform-loinc.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T22:20:02+00:00</t>
+    <t>2026-09-17T12:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
